--- a/outputs/forecasts/xgboost_evaluation_metrics.xlsx
+++ b/outputs/forecasts/xgboost_evaluation_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>mape</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,6 +498,9 @@
       <c r="H2" t="n">
         <v>16.5001</v>
       </c>
+      <c r="I2" t="n">
+        <v>-0.9409999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -525,6 +533,9 @@
       <c r="H3" t="n">
         <v>18.8917</v>
       </c>
+      <c r="I3" t="n">
+        <v>-24.6707</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,6 +568,9 @@
       <c r="H4" t="n">
         <v>10.8376</v>
       </c>
+      <c r="I4" t="n">
+        <v>-0.497</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -589,6 +603,9 @@
       <c r="H5" t="n">
         <v>20.0432</v>
       </c>
+      <c r="I5" t="n">
+        <v>-1.22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -621,6 +638,9 @@
       <c r="H6" t="n">
         <v>17.5899</v>
       </c>
+      <c r="I6" t="n">
+        <v>0.3909</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -653,6 +673,9 @@
       <c r="H7" t="n">
         <v>23.3946</v>
       </c>
+      <c r="I7" t="n">
+        <v>-105.4697</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -685,6 +708,9 @@
       <c r="H8" t="n">
         <v>17.0391</v>
       </c>
+      <c r="I8" t="n">
+        <v>-1.3657</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -717,6 +743,9 @@
       <c r="H9" t="n">
         <v>4.6362</v>
       </c>
+      <c r="I9" t="n">
+        <v>0.3716</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -749,6 +778,9 @@
       <c r="H10" t="n">
         <v>3.8296</v>
       </c>
+      <c r="I10" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -781,6 +813,9 @@
       <c r="H11" t="n">
         <v>53.4548</v>
       </c>
+      <c r="I11" t="n">
+        <v>-5.1101</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -813,6 +848,9 @@
       <c r="H12" t="n">
         <v>15.7007</v>
       </c>
+      <c r="I12" t="n">
+        <v>-1.3447</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -845,6 +883,9 @@
       <c r="H13" t="n">
         <v>7.1878</v>
       </c>
+      <c r="I13" t="n">
+        <v>0.825</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -877,6 +918,9 @@
       <c r="H14" t="n">
         <v>1.7329</v>
       </c>
+      <c r="I14" t="n">
+        <v>0.9341</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -909,6 +953,9 @@
       <c r="H15" t="n">
         <v>5.072</v>
       </c>
+      <c r="I15" t="n">
+        <v>0.7213000000000001</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -941,6 +988,9 @@
       <c r="H16" t="n">
         <v>15.0033</v>
       </c>
+      <c r="I16" t="n">
+        <v>0.0515</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -973,6 +1023,7 @@
       <c r="H17" t="n">
         <v>46.6418</v>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1005,6 +1056,9 @@
       <c r="H18" t="n">
         <v>19.4995</v>
       </c>
+      <c r="I18" t="n">
+        <v>-0.1435</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1037,6 +1091,9 @@
       <c r="H19" t="n">
         <v>22.1911</v>
       </c>
+      <c r="I19" t="n">
+        <v>-316.7495</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1069,6 +1126,7 @@
       <c r="H20" t="n">
         <v>46.237</v>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1101,6 +1159,9 @@
       <c r="H21" t="n">
         <v>12.2352</v>
       </c>
+      <c r="I21" t="n">
+        <v>-0.338</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1132,6 +1193,9 @@
       </c>
       <c r="H22" t="n">
         <v>12.9149</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6784</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/forecasts/xgboost_evaluation_metrics.xlsx
+++ b/outputs/forecasts/xgboost_evaluation_metrics.xlsx
@@ -525,16 +525,16 @@
         <v>2.73</v>
       </c>
       <c r="F3" t="n">
-        <v>4374.1875</v>
+        <v>4584.0792</v>
       </c>
       <c r="G3" t="n">
-        <v>5514.0422</v>
+        <v>5601.7111</v>
       </c>
       <c r="H3" t="n">
-        <v>18.8917</v>
+        <v>19.3356</v>
       </c>
       <c r="I3" t="n">
-        <v>-24.6707</v>
+        <v>-24.6874</v>
       </c>
     </row>
     <row r="4">
@@ -630,16 +630,16 @@
         <v>2.6</v>
       </c>
       <c r="F6" t="n">
-        <v>2607.837</v>
+        <v>3237.512</v>
       </c>
       <c r="G6" t="n">
-        <v>3215.3269</v>
+        <v>3478.3335</v>
       </c>
       <c r="H6" t="n">
-        <v>17.5899</v>
+        <v>18.9216</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3909</v>
+        <v>0.3369</v>
       </c>
     </row>
     <row r="7">
@@ -980,16 +980,16 @@
         <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>8580.570299999999</v>
+        <v>11728.9453</v>
       </c>
       <c r="G16" t="n">
-        <v>11173.9171</v>
+        <v>12488.95</v>
       </c>
       <c r="H16" t="n">
-        <v>15.0033</v>
+        <v>21.6618</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0515</v>
+        <v>-0.1645</v>
       </c>
     </row>
     <row r="17">
